--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32200,7 +32200,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -32828,7 +32828,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -35002,7 +35002,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
